--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486361_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486361_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1585</v>
+        <v>6.6672</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5931</v>
+        <v>3.0401</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5654</v>
+        <v>3.627</v>
       </c>
       <c r="G2" t="n">
         <v>1.9517</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.577</v>
+        <v>1.0857</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3869</v>
+        <v>0.0601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.964</v>
+        <v>1.0256</v>
       </c>
       <c r="V2" t="n">
         <v>3.1947</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9559</v>
+        <v>5.3137</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0397</v>
+        <v>5.1144</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0838</v>
+        <v>0.1992</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6742</v>
+        <v>4.1074</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2168</v>
+        <v>2.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4574</v>
+        <v>1.6774</v>
       </c>
       <c r="J3" t="n">
-        <v>2.676</v>
+        <v>4.9801</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5612</v>
+        <v>3.0294</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>1.9507</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0018</v>
+        <v>-0.8727</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3444</v>
+        <v>-0.5994</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3426</v>
+        <v>-0.2733</v>
       </c>
       <c r="P3" t="n">
         <v>0.87</v>
@@ -688,28 +688,28 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1719</v>
+        <v>0.706</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3638</v>
+        <v>0.3088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8081</v>
+        <v>0.3972</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7602</v>
+        <v>-0.3698</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5014</v>
+        <v>2.8857</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4871</v>
+        <v>3.4319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0143</v>
+        <v>-0.5462</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1074</v>
+        <v>1.6742</v>
       </c>
       <c r="H4" t="n">
-        <v>2.43</v>
+        <v>1.2168</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6774</v>
+        <v>0.4574</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9801</v>
+        <v>2.676</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0294</v>
+        <v>2.5612</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9507</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8727</v>
+        <v>-1.0018</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5994</v>
+        <v>-1.3444</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2733</v>
+        <v>0.3426</v>
       </c>
       <c r="P4" t="n">
         <v>0.87</v>
@@ -766,28 +766,28 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1062</v>
+        <v>1.1017</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3184</v>
+        <v>0.7559</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2122</v>
+        <v>0.3458</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1898</v>
+        <v>2.5589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2605</v>
+        <v>1.5903</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9293</v>
+        <v>0.9685</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5495</v>
+        <v>1.9745</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8452</v>
+        <v>-2.2353</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2957</v>
+        <v>4.2098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9577</v>
+        <v>3.4616</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7665</v>
+        <v>-1.3195</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1912</v>
+        <v>4.7812</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4082</v>
+        <v>-1.4872</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4869</v>
+        <v>-0.5714</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9576</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9028</v>
+        <v>0.977</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2402</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6626</v>
+        <v>0.9109</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
         <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9226</v>
+        <v>1.9759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8512999999999999</v>
+        <v>-0.5218</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0713</v>
+        <v>2.4978</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9745</v>
+        <v>0.5495</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2353</v>
+        <v>0.8452</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2098</v>
+        <v>-0.2957</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4616</v>
+        <v>0.9577</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3195</v>
+        <v>0.7665</v>
       </c>
       <c r="L6" t="n">
-        <v>4.7812</v>
+        <v>0.1912</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4872</v>
+        <v>-0.4082</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5714</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5225</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3407</v>
+        <v>1.689</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.4579</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0136</v>
+        <v>1.2311</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="W6" t="n">
         <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5516</v>
+        <v>0.7218</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4127</v>
+        <v>1.7332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1389</v>
+        <v>-1.0114</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8545</v>
+        <v>1.719</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7238</v>
+        <v>0.3739</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1307</v>
+        <v>1.3451</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1046</v>
+        <v>1.5956</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1428</v>
+        <v>1.0402</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>0.5554</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7499</v>
+        <v>0.1233</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.581</v>
+        <v>-0.6663</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1689</v>
+        <v>0.7897</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7536</v>
+        <v>0.545</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5396</v>
+        <v>-0.0577</v>
       </c>
       <c r="U7" t="n">
-        <v>0.214</v>
+        <v>0.6026</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.6297</v>
       </c>
       <c r="W7" t="n">
         <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.194</v>
+        <v>0.5091</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0033</v>
+        <v>2.0718</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8093</v>
+        <v>-1.5627</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9209000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2449</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1406</v>
+        <v>0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1043</v>
+        <v>0.3509</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0832</v>
+        <v>0.3589</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0739</v>
+        <v>0.1892</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9907</v>
+        <v>0.1697</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.888</v>
+        <v>-0.8545</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2858</v>
+        <v>-0.7238</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1738</v>
+        <v>-0.1307</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2297</v>
+        <v>-0.1046</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2222</v>
+        <v>-0.1428</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4519</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3417</v>
+        <v>-0.7499</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0636</v>
+        <v>-0.581</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>-0.1689</v>
       </c>
       <c r="P9" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4572</v>
+        <v>0.5609</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2656</v>
+        <v>0.316</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1917</v>
+        <v>0.2448</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1453</v>
+        <v>0.1965</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1744</v>
+        <v>0.4798</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3197</v>
+        <v>-0.2834</v>
       </c>
       <c r="G10" t="n">
-        <v>1.719</v>
+        <v>0.8952</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3739</v>
+        <v>-1.6818</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3451</v>
+        <v>2.577</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5956</v>
+        <v>2.5314</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0402</v>
+        <v>-0.319</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5554</v>
+        <v>2.8504</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1233</v>
+        <v>-1.6362</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6663</v>
+        <v>-1.3628</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7897</v>
+        <v>-0.2733</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3221</v>
+        <v>0.1511</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>0.1034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2944</v>
+        <v>0.0478</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6297</v>
+        <v>1.3252</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5849</v>
+        <v>-0.2644</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1474</v>
+        <v>-2.4092</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4375</v>
+        <v>2.1448</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8952</v>
+        <v>-0.888</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6818</v>
+        <v>0.2858</v>
       </c>
       <c r="I11" t="n">
-        <v>2.577</v>
+        <v>-1.1738</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5314</v>
+        <v>-1.2297</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.319</v>
+        <v>0.2222</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8504</v>
+        <v>-1.4519</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6362</v>
+        <v>0.3417</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3628</v>
+        <v>0.0636</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2733</v>
+        <v>0.2781</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4801</v>
+        <v>-1.305</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6303</v>
+        <v>0.2761</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5239</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1064</v>
+        <v>0.3458</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.849</v>
+        <v>-0.8605</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9443</v>
+        <v>-0.8326</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0953</v>
+        <v>-0.028</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9603</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1113</v>
+        <v>0.0997</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1113</v>
+        <v>-0.012</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.284</v>
+        <v>-1.1414</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9443</v>
+        <v>-0.8326</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3397</v>
+        <v>-0.3088</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9603</v>
@@ -1468,13 +1468,13 @@
         <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1285</v>
+        <v>0.0141</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.5274</v>
+        <v>18.9214</v>
       </c>
       <c r="E14" t="n">
-        <v>12.7122</v>
+        <v>13.0545</v>
       </c>
       <c r="F14" t="n">
-        <v>5.815200000000001</v>
+        <v>5.8665</v>
       </c>
       <c r="G14" t="n">
-        <v>8.287499999999998</v>
+        <v>8.2875</v>
       </c>
       <c r="H14" t="n">
-        <v>3.817299999999999</v>
+        <v>3.8173</v>
       </c>
       <c r="I14" t="n">
         <v>4.4703</v>
@@ -1525,10 +1525,10 @@
         <v>10.1458</v>
       </c>
       <c r="L14" t="n">
-        <v>5.6138</v>
+        <v>5.613799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.4724</v>
+        <v>-7.472400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-6.3285</v>
@@ -1546,13 +1546,13 @@
         <v>11.9626</v>
       </c>
       <c r="S14" t="n">
-        <v>7.3723</v>
+        <v>7.7663</v>
       </c>
       <c r="T14" t="n">
-        <v>2.031199999999999</v>
+        <v>2.3735</v>
       </c>
       <c r="U14" t="n">
-        <v>5.3413</v>
+        <v>5.3929</v>
       </c>
       <c r="V14" t="n">
         <v>3.955</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5027</v>
+        <v>3.3338</v>
       </c>
       <c r="E15" t="n">
-        <v>3.854</v>
+        <v>4.4128</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3513</v>
+        <v>-1.079</v>
       </c>
       <c r="G15" t="n">
         <v>2.8081</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7828</v>
+        <v>-0.9517</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2329</v>
+        <v>-0.6741</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.2776</v>
       </c>
       <c r="V15" t="n">
         <v>1.695</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6099</v>
+        <v>0.7158</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.0237</v>
       </c>
       <c r="F16" t="n">
         <v>0.6921</v>
@@ -1702,10 +1702,10 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9181</v>
+        <v>0.024</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8736</v>
+        <v>-0.0204</v>
       </c>
       <c r="U16" t="n">
         <v>0.0445</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4429</v>
+        <v>-0.7313</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8327</v>
+        <v>-1.6092</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3898</v>
+        <v>0.8779</v>
       </c>
       <c r="G18" t="n">
         <v>0.2868</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6644</v>
+        <v>0.0472</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2139</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4505</v>
+        <v>0.0375</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7029</v>
+        <v>-1.7337</v>
       </c>
       <c r="E19" t="n">
         <v>-1.9629</v>
       </c>
       <c r="F19" t="n">
-        <v>0.26</v>
+        <v>0.2292</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7852</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1575</v>
+        <v>-0.1884</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0121</v>
+        <v>-0.043</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7979</v>
+        <v>-1.9351</v>
       </c>
       <c r="E20" t="n">
-        <v>1.082</v>
+        <v>-1.7234</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8799</v>
+        <v>-0.2118</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0003</v>
+        <v>-1.4466</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1373</v>
+        <v>-1.3016</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1371</v>
+        <v>-0.145</v>
       </c>
       <c r="J20" t="n">
-        <v>1.063</v>
+        <v>-0.3444</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3745</v>
+        <v>-0.1547</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6885</v>
+        <v>-0.1896</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0633</v>
+        <v>-1.1022</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5118</v>
+        <v>-1.1468</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5514</v>
+        <v>0.0446</v>
       </c>
       <c r="P20" t="n">
         <v>-0.2175</v>
@@ -2014,28 +2014,28 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0358</v>
+        <v>-0.4663</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3257</v>
+        <v>-0.4867</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3615</v>
+        <v>0.0204</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5443</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7809</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3219</v>
+        <v>-2.2205</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0586</v>
+        <v>0.2997</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2632</v>
+        <v>-2.5202</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4466</v>
+        <v>-1.0003</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3016</v>
+        <v>-1.1373</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.145</v>
+        <v>0.1371</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3444</v>
+        <v>1.063</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1547</v>
+        <v>0.3745</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1896</v>
+        <v>0.6885</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1022</v>
+        <v>-2.0633</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1468</v>
+        <v>-1.5118</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0446</v>
+        <v>-0.5514</v>
       </c>
       <c r="P21" t="n">
         <v>-0.2175</v>
@@ -2092,22 +2092,22 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.853</v>
+        <v>-0.4584</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.4566</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.031</v>
+        <v>-0.0018</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-0.5443</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0.7809</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4534</v>
+        <v>-2.5151</v>
       </c>
       <c r="E22" t="n">
         <v>-1.7286</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7248</v>
+        <v>-0.7865</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2721</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8991</v>
+        <v>-0.9608</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4194</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4797</v>
+        <v>-0.5414</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9586</v>
+        <v>-3.2508</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8796</v>
+        <v>-2.3208</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.079</v>
+        <v>-0.93</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8369</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.579</v>
+        <v>-0.8712</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4384</v>
+        <v>-0.8796</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1406</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3241</v>
+        <v>-4.3793</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7146</v>
+        <v>-0.8263</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6095</v>
+        <v>-3.553</v>
       </c>
       <c r="G24" t="n">
         <v>-2.932</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0446</v>
+        <v>-1.0998</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9673</v>
+        <v>-1.0791</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0207</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9745</v>
+        <v>-4.6572</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4234</v>
+        <v>-0.3117</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5511</v>
+        <v>-4.3456</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1837</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2057</v>
+        <v>-0.8883</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2329</v>
+        <v>-1.1212</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0273</v>
+        <v>0.2328</v>
       </c>
       <c r="V25" t="n">
         <v>-3.5851</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.5273</v>
+        <v>-17.0371</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.815100000000001</v>
+        <v>-5.8152</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.7121</v>
+        <v>-11.2221</v>
       </c>
       <c r="G26" t="n">
         <v>-8.287599999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.8173</v>
+        <v>-3.817299999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-4.4703</v>
@@ -2482,13 +2482,13 @@
         <v>13.0503</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.3723</v>
+        <v>-5.8822</v>
       </c>
       <c r="T26" t="n">
         <v>-5.3414</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.030800000000001</v>
+        <v>-0.5409</v>
       </c>
       <c r="V26" t="n">
         <v>-3.9547</v>
